--- a/dataset_t6_grouped/results2/G3/G3_T7503_W0058F0001T0006Z000C1N34_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G3/G3_T7503_W0058F0001T0006Z000C1N34_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>20.32947875897388</v>
+        <v>3.303540298333256</v>
       </c>
       <c r="D2" t="n">
-        <v>3.599893598650866</v>
+        <v>0.5849827097807657</v>
       </c>
       <c r="E2" t="n">
-        <v>16.35002684714079</v>
+        <v>2.656879362660378</v>
       </c>
       <c r="F2" t="n">
-        <v>17.69962337746674</v>
+        <v>2.876188798838345</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>18.32265059409768</v>
+        <v>2.977430721540873</v>
       </c>
       <c r="D3" t="n">
-        <v>17.360337786853</v>
+        <v>2.821054890363613</v>
       </c>
       <c r="E3" t="n">
-        <v>16.35002684714079</v>
+        <v>2.656879362660378</v>
       </c>
       <c r="F3" t="n">
-        <v>17.69962337746674</v>
+        <v>2.876188798838345</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>46.40961576943669</v>
+        <v>7.541562562533462</v>
       </c>
       <c r="D4" t="n">
-        <v>24.5001417229461</v>
+        <v>3.981273029978742</v>
       </c>
       <c r="E4" t="n">
-        <v>16.35002684714079</v>
+        <v>2.656879362660378</v>
       </c>
       <c r="F4" t="n">
-        <v>17.69962337746674</v>
+        <v>2.876188798838345</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>61.53777868339987</v>
+        <v>9.99988903605248</v>
       </c>
       <c r="D5" t="n">
-        <v>47.29206135208014</v>
+        <v>7.684959969713023</v>
       </c>
       <c r="E5" t="n">
-        <v>16.35002684714079</v>
+        <v>2.656879362660378</v>
       </c>
       <c r="F5" t="n">
-        <v>17.69962337746674</v>
+        <v>2.876188798838345</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>41.61401632207143</v>
+        <v>6.762277652336607</v>
       </c>
       <c r="D6" t="n">
-        <v>49.7869875797846</v>
+        <v>8.090385481714998</v>
       </c>
       <c r="E6" t="n">
-        <v>16.35002684714079</v>
+        <v>2.656879362660378</v>
       </c>
       <c r="F6" t="n">
-        <v>17.69962337746674</v>
+        <v>2.876188798838345</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
